--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260810.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.93%</t>
+          <t>9.87%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.68%</t>
+          <t>8.95%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.02%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.13%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.79%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>442,925,000</t>
+          <t>5,037,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>5,037,000</t>
+          <t>448,725,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>361,389,964</t>
+          <t>362,939,964</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -858,46 +858,46 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>31,356,000</t>
+          <t>63,040,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>131,819,945</t>
+          <t>31,356,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,127 +909,127 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>131,819,945</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>63,040,000</t>
+          <t>26,144,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>202,817,000</t>
+          <t>82,730,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,144,000</t>
+          <t>230,616,516</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>82,730,000</t>
+          <t>97,953,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>145,652,000</t>
+          <t>202,817,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,44 +1041,44 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>131,978,000</t>
+          <t>145,652,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>97,953,442</t>
+          <t>131,978,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -1144,24 +1144,24 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>55,187,000</t>
+          <t>188,180,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,44 +1173,44 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>273,066,000</t>
+          <t>55,187,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>188,180,000</t>
+          <t>273,066,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,930,374,237</t>
+          <t>13,830,852,234</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,355,419,583</t>
+          <t>4,640,381,183</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-52,184,644</t>
+          <t>-22,447,244</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
